--- a/artfynd/A 63479-2023 artfynd.xlsx
+++ b/artfynd/A 63479-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63479-2023 artfynd.xlsx
+++ b/artfynd/A 63479-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,6 +798,113 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129850106</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58018</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Södra Stadsskogen, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>352102</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6422101</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Måttliga förekomster, flera</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Gabriella Samuelsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Gabriella Samuelsson, Pia Edfors, Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63479-2023 artfynd.xlsx
+++ b/artfynd/A 63479-2023 artfynd.xlsx
@@ -901,7 +901,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gabriella Samuelsson, Pia Edfors, Sofia Berg</t>
+          <t>Sofia Berg, Pia Edfors, Gabriella Samuelsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 63479-2023 artfynd.xlsx
+++ b/artfynd/A 63479-2023 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>129850106</v>
       </c>
       <c r="B3" t="n">
-        <v>58018</v>
+        <v>58019</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sofia Berg, Pia Edfors, Gabriella Samuelsson</t>
+          <t>Gabriella Samuelsson, Pia Edfors, Sofia Berg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 63479-2023 artfynd.xlsx
+++ b/artfynd/A 63479-2023 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>129850106</v>
       </c>
       <c r="B3" t="n">
-        <v>58019</v>
+        <v>58022</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63479-2023 artfynd.xlsx
+++ b/artfynd/A 63479-2023 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>129850106</v>
       </c>
       <c r="B3" t="n">
-        <v>58022</v>
+        <v>58023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sofia Berg, Pia Edfors, Gabriella Samuelsson</t>
+          <t>Gabriella Samuelsson, Pia Edfors, Sofia Berg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 63479-2023 artfynd.xlsx
+++ b/artfynd/A 63479-2023 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>129850106</v>
       </c>
       <c r="B3" t="n">
-        <v>58024</v>
+        <v>58109</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63479-2023 artfynd.xlsx
+++ b/artfynd/A 63479-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89827114</v>
+        <v>89827095</v>
       </c>
       <c r="B2" t="n">
-        <v>57007</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58238</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103042</v>
+        <v>103012</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>352231.0392801253</v>
+        <v>352229</v>
       </c>
       <c r="R2" t="n">
-        <v>6422054.818560242</v>
+        <v>6422016</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,22 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-04-24</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-05-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-04-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-05-30</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -801,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129850106</v>
+        <v>129850089</v>
       </c>
       <c r="B3" t="n">
-        <v>58024</v>
+        <v>58238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>352102</v>
+        <v>352236</v>
       </c>
       <c r="R3" t="n">
-        <v>6422101</v>
+        <v>6422033</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +866,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Måttliga förekomster, flera</t>
+          <t>Sång</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,10 +886,339 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sofia Berg, Pia Edfors, Gabriella Samuelsson</t>
+          <t>Gabriella Samuelsson, Sofia Berg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129850106</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58238</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Södra Stadsskogen, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>352102</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6422101</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Måttliga förekomster, flera</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Gabriella Samuelsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Gabriella Samuelsson, Pia Edfors, Sofia Berg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>89827114</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Alingsås, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>352231</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6422055</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-04-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-04-24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>EOT0017 Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erik Edvardsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>89827234</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Alingsås, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>352237</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6422073</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-04-24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-04-24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>EOT0017 Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erik Edvardsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63479-2023 artfynd.xlsx
+++ b/artfynd/A 63479-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89827095</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129850089</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129850106</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89827114</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1219,8 +1244,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89827234</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>